--- a/Voti_Fantacalcio/Voti_Fantacalcio_Stagione_2023_24_Giornata_22.xlsx
+++ b/Voti_Fantacalcio/Voti_Fantacalcio_Stagione_2023_24_Giornata_22.xlsx
@@ -658,7 +658,7 @@
     <t>Pierotti</t>
   </si>
   <si>
-    <t>D'aversa</t>
+    <t>D'Aversa</t>
   </si>
   <si>
     <t>Milan</t>
@@ -724,7 +724,7 @@
     <t>Izzo</t>
   </si>
   <si>
-    <t>D'ambrosio</t>
+    <t>D'Ambrosio</t>
   </si>
   <si>
     <t>Bettella</t>
